--- a/身体状态记录.xlsx
+++ b/身体状态记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wujiazhai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15102E67-801C-40E3-874B-C228996CC773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A580E5-F630-4A7C-822E-E9F0225EFEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -527,11 +527,23 @@
       <c r="A12" s="4">
         <v>45820</v>
       </c>
+      <c r="B12" s="5">
+        <v>126.1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>85</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>45821</v>
       </c>
+      <c r="B13" s="5">
+        <v>127.7</v>
+      </c>
+      <c r="C13" s="5">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
@@ -541,6 +553,12 @@
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>45823</v>
+      </c>
+      <c r="B15" s="5">
+        <v>125.8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>84.5</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">

--- a/身体状态记录.xlsx
+++ b/身体状态记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wujiazhai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A580E5-F630-4A7C-822E-E9F0225EFEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1611FFB-443D-4F76-9184-43EB6A90DDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -36,6 +36,18 @@
   </si>
   <si>
     <t>腰围（CM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是量肚脐眼上方两厘米的位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短袖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>170 m</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -392,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="4" customWidth="1"/>
@@ -402,7 +414,7 @@
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -412,8 +424,11 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>45810</v>
       </c>
@@ -423,8 +438,11 @@
       <c r="C2" s="5">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>45811</v>
       </c>
@@ -435,7 +453,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>45812</v>
       </c>
@@ -446,7 +464,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>45813</v>
       </c>
@@ -457,7 +475,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>45814</v>
       </c>
@@ -468,7 +486,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>45815</v>
       </c>
@@ -479,7 +497,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>45816</v>
       </c>
@@ -490,7 +508,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>45817</v>
       </c>
@@ -501,7 +519,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>45818</v>
       </c>
@@ -512,7 +530,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>45819</v>
       </c>
@@ -523,7 +541,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>45820</v>
       </c>
@@ -534,7 +552,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>45821</v>
       </c>
@@ -545,12 +563,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>45822</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>45823</v>
       </c>
@@ -561,22 +579,37 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>45824</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B16" s="5">
+        <v>125.3</v>
+      </c>
+      <c r="C16" s="5">
+        <v>83.5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>45825</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B17" s="5">
+        <v>125.6</v>
+      </c>
+      <c r="C17" s="5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>45826</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>45827</v>
       </c>

--- a/身体状态记录.xlsx
+++ b/身体状态记录.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wujiazhai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1611FFB-443D-4F76-9184-43EB6A90DDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F08F59-56FF-4B3C-8069-E1F7E91190DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="4" customWidth="1"/>
@@ -608,10 +608,202 @@
       <c r="A18" s="4">
         <v>45826</v>
       </c>
+      <c r="B18" s="5">
+        <v>123.6</v>
+      </c>
+      <c r="C18" s="5">
+        <v>82.5</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>45827</v>
+      </c>
+      <c r="B19" s="5">
+        <v>123.2</v>
+      </c>
+      <c r="C19" s="5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>45829</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>45830</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>45831</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>45832</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>45834</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>45835</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>45836</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>45837</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>45838</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>45840</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>45841</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>45842</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>45843</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>45844</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>45845</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>45846</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>45847</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>45848</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
+        <v>45849</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>45850</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
+        <v>45851</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
+        <v>45854</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
+        <v>45855</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>45856</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>45857</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>45858</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>45859</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>45860</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>45861</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>45862</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>45863</v>
       </c>
     </row>
   </sheetData>

--- a/身体状态记录.xlsx
+++ b/身体状态记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wujiazhai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F08F59-56FF-4B3C-8069-E1F7E91190DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06344573-F67A-48DE-8175-977419AF0D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,6 +630,12 @@
       <c r="A20" s="4">
         <v>45828</v>
       </c>
+      <c r="B20" s="5">
+        <v>123.1</v>
+      </c>
+      <c r="C20" s="5">
+        <v>80.5</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
@@ -640,6 +646,12 @@
       <c r="A22" s="4">
         <v>45830</v>
       </c>
+      <c r="B22" s="5">
+        <v>123.6</v>
+      </c>
+      <c r="C22" s="5">
+        <v>80.3</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
@@ -654,6 +666,12 @@
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>45833</v>
+      </c>
+      <c r="B25" s="5">
+        <v>122.5</v>
+      </c>
+      <c r="C25" s="5">
+        <v>80.5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
